--- a/samples/ss_ksghn_ingest.xlsx
+++ b/samples/ss_ksghn_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,65 +535,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -632,24 +637,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -685,41 +691,46 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>KSGHN7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>KSGHN</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT x 500 MVA (unit 1,2)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -752,30 +763,31 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -808,34 +820,35 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>SST 40 MVA; outlet tower combined</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -868,30 +881,31 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>2x300 MW</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -924,30 +938,31 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>U3 660 MW + U4 945 MW</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -980,34 +995,35 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>single phi; 20/60/30 MVA + KTT Pertamina</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1040,34 +1056,35 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>single phi di GI Lomanis</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1100,30 +1117,31 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>2x60 MVA + KTT SBI</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1156,34 +1174,35 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>60/30 MVA</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1216,34 +1235,35 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>30/20/60/60/60 MVA</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1276,30 +1296,31 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>PLTA 8,3 MW</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1332,34 +1353,35 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1392,34 +1414,35 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1452,34 +1475,35 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pemalang 1,2</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1512,34 +1536,35 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>3x60 MVA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1572,34 +1597,35 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>PLTA Mrica; bay A1-A5 / B1-B4</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1632,34 +1658,35 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>30 MVA</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1692,34 +1719,35 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>single phi + single busbar; aset PT Geo Dipa Energi</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1752,34 +1780,35 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>74,5 MVA + 30 MVA</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1812,34 +1841,35 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>60/20/30 MVA + SMPOR 1 MW</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1872,34 +1902,35 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>30/60/60 MVA</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1932,34 +1963,35 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>30/60 MVA</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1992,38 +2024,39 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>batas ke GI Bantul / Subsistem Pedan</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2056,30 +2089,31 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>16 MVA + PJKLN 1,4 MW + U1,U2 8 MW</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2112,30 +2146,31 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>20/30/60 MVA; arah BNJAR SS Tasik</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2168,30 +2203,31 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Jawa Tengah</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_ksghn_ingest.xlsx
+++ b/samples/ss_ksghn_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_ksghn_ingest.xlsx
+++ b/samples/ss_ksghn_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Kesugihan 500/150 kV</t>
+          <t>IBT 1 Kesugihan 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT x 500 MVA (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,37 +734,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kesugihan (bus 150 kV)</t>
+          <t>IBT 2 Kesugihan 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 KSGHN7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KSGHN7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>KSGHN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2x60 MVA</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -778,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -795,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cilacap (bus PLTU)</t>
+          <t>Kesugihan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>KSGHN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -809,7 +819,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -823,7 +833,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SST 40 MVA; outlet tower combined</t>
+          <t>2x60 MVA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -835,14 +845,10 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -856,17 +862,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTU Cilacap U1,U2</t>
+          <t>Cilacap (bus PLTU)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_CLCAP</t>
+          <t>CLCAP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -884,7 +890,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2x300 MW</t>
+          <t>SST 40 MVA; outlet tower combined</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -896,10 +902,14 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -913,12 +923,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLTU Cilacap U3,U4</t>
+          <t>PLTU Cilacap U1,U2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_CLCAP34</t>
+          <t>KIT_CLCAP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -941,7 +951,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>U3 660 MW + U4 945 MW</t>
+          <t>2x300 MW</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -970,21 +980,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lomanis</t>
+          <t>PLTU Cilacap U3,U4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LMNIS</t>
+          <t>KIT_CLCAP34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -998,7 +1008,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>single phi; 20/60/30 MVA + KTT Pertamina</t>
+          <t>U3 660 MW + U4 945 MW</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1010,14 +1020,10 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1031,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Semen Nusantara</t>
+          <t>Lomanis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SMNUS</t>
+          <t>LMNIS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1059,7 +1065,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>single phi di GI Lomanis</t>
+          <t>single phi; 20/60/30 MVA + KTT Pertamina</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1076,7 +1082,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1092,12 +1098,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sitanala / Stara</t>
+          <t>Semen Nusantara</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STARA</t>
+          <t>SMNUS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1120,7 +1126,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2x60 MVA + KTT SBI</t>
+          <t>single phi di GI Lomanis</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1132,10 +1138,14 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1149,12 +1159,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rawalo</t>
+          <t>Sitanala / Stara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RWALO</t>
+          <t>STARA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1163,7 +1173,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1177,7 +1187,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>60/30 MVA</t>
+          <t>2x60 MVA + KTT SBI</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1189,14 +1199,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1210,12 +1216,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kalibakal</t>
+          <t>Rawalo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KLBKL</t>
+          <t>RWALO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1224,7 +1230,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1238,7 +1244,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30/20/60/60/60 MVA</t>
+          <t>60/30 MVA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1255,7 +1261,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1271,12 +1277,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Katenger</t>
+          <t>Kalibakal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KTNGR</t>
+          <t>KLBKL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1285,7 +1291,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1299,7 +1305,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PLTA 8,3 MW</t>
+          <t>30/20/60/60/60 MVA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1311,10 +1317,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1328,12 +1338,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bumiayu</t>
+          <t>Katenger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BMAYU</t>
+          <t>KTNGR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1356,7 +1366,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>60 MVA</t>
+          <t>PLTA 8,3 MW</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1368,14 +1378,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1389,12 +1395,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Balapulang</t>
+          <t>Bumiayu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BLPLG</t>
+          <t>BMAYU</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1403,7 +1409,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1417,7 +1423,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2x60 MVA</t>
+          <t>60 MVA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1434,7 +1440,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1450,12 +1456,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kebasen</t>
+          <t>Balapulang</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KBSEN</t>
+          <t>BLPLG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1464,7 +1470,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1478,7 +1484,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Pemalang 1,2</t>
+          <t>2x60 MVA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1487,17 +1493,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1511,12 +1517,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Purbalingga</t>
+          <t>Kebasen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PBLGA</t>
+          <t>KBSEN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1525,7 +1531,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1539,7 +1545,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3x60 MVA</t>
+          <t>batas ke Subsistem Pemalang 1,2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1548,17 +1554,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1572,12 +1578,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PLTA Mrica</t>
+          <t>Purbalingga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MRICA</t>
+          <t>PBLGA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1586,7 +1592,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1600,7 +1606,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PLTA Mrica; bay A1-A5 / B1-B4</t>
+          <t>3x60 MVA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1617,7 +1623,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1633,12 +1639,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wonosobo</t>
+          <t>PLTA Mrica</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WSOBO</t>
+          <t>MRICA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1647,7 +1653,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1661,7 +1667,7 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30 MVA</t>
+          <t>PLTA Mrica; bay A1-A5 / B1-B4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1678,7 +1684,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1694,12 +1700,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Garung</t>
+          <t>Wonosobo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GARNG</t>
+          <t>WSOBO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1708,7 +1714,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1722,7 +1728,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>single phi + single busbar; aset PT Geo Dipa Energi</t>
+          <t>30 MVA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1739,7 +1745,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1755,12 +1761,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PLTP Dieng</t>
+          <t>Garung</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIENG</t>
+          <t>GARNG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1783,7 +1789,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>74,5 MVA + 30 MVA</t>
+          <t>single phi + single busbar; aset PT Geo Dipa Energi</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1800,7 +1806,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1816,12 +1822,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gombong</t>
+          <t>PLTP Dieng</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GBONG</t>
+          <t>DIENG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1830,7 +1836,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1850,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>60/20/30 MVA + SMPOR 1 MW</t>
+          <t>74,5 MVA + 30 MVA</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1861,7 +1867,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1877,12 +1883,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kebumen</t>
+          <t>Gombong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KBMEN</t>
+          <t>GBONG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1891,7 +1897,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1905,7 +1911,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30/60/60 MVA</t>
+          <t>60/20/30 MVA + SMPOR 1 MW</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1922,7 +1928,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -1938,12 +1944,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Purworejo</t>
+          <t>Kebumen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PWRJO</t>
+          <t>KBMEN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1952,7 +1958,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1966,7 +1972,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30/60 MVA</t>
+          <t>30/60/60 MVA</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1983,7 +1989,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -1999,12 +2005,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wates</t>
+          <t>Purworejo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WATES</t>
+          <t>PWRJO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2013,7 +2019,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2027,7 +2033,7 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>batas ke GI Bantul / Subsistem Pedan</t>
+          <t>30/60 MVA</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2036,11 +2042,7 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2064,12 +2066,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wadaslintang</t>
+          <t>Wates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WDLTG</t>
+          <t>WATES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2078,7 +2080,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2092,7 +2094,7 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>16 MVA + PJKLN 1,4 MW + U1,U2 8 MW</t>
+          <t>batas ke GI Bantul / Subsistem Pedan</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2101,13 +2103,21 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2121,12 +2131,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Majenang</t>
+          <t>Wadaslintang</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MNANG</t>
+          <t>WDLTG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2135,7 +2145,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2159,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>20/30/60 MVA; arah BNJAR SS Tasik</t>
+          <t>16 MVA + PJKLN 1,4 MW + U1,U2 8 MW</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2178,12 +2188,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sidareja / Start</t>
+          <t>Majenang</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>START</t>
+          <t>MNANG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2206,7 +2216,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>60 MVA</t>
+          <t>20/30/60 MVA; arah BNJAR SS Tasik</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2228,6 +2238,63 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sidareja / Start</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>60 MVA</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4147,12 +4214,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Rawalo- Purbalingga 1,2 atau Mrica-Wonosobo 1,2trip 2 sirkit (N-1-1/N-2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
+          <t>[N-1-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Rawalo- Purbalingga 1,2 atau Mrica-Wonosobo 1,2trip 2 sirkit (N-1-1/N-2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4182,12 +4249,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Kesugihan- Gombong 1,2 atau Kebumen-Gombong trip 2 sirkit (N-1-1/N-2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
+          <t>[N-1-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Kesugihan- Gombong 1,2 atau Kebumen-Gombong trip 2 sirkit (N-1-1/N-2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4217,12 +4284,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] Konfigurasi SUTT 150 kV Kalibakal-Cilacap dan Rawalo - Kalibakalmasih singlephisehinggakurang andal</t>
+          <t>[BELUM_DITETAPKAN] Konfigurasi SUTT 150 kV Kalibakal-Cilacap dan Rawalo - Kalibakalmasih singlephisehinggakurang andal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4252,12 +4319,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] 1.Konfigurasi SUTT 150 kV Kesugihan-Semen Nusantara &amp; Kesugihan-Lomanis masih single phi di GI Lomanis. 2.Terjadi pembebanan &gt;60% pada ruas Kesugihan-Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi</t>
+          <t>[BELUM_DITETAPKAN] 1.Konfigurasi SUTT 150 kV Kesugihan-Semen Nusantara &amp; Kesugihan-Lomanis masih single phi di GI Lomanis. 2.Terjadi pembebanan &gt;60% pada ruas Kesugihan-Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4287,12 +4354,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi pembebanan &gt;60% pada ruas Kesugihan-Semen Nusantara apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi</t>
+          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan-Semen Nusantara apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4392,12 +4459,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] 1.GI 150 kV Garung (aset PT Geodipa Energi) beroperasi single phi dan single Busbar. 2.Tidak ada PMT 150 kV arah PLTA Garung</t>
+          <t>[BELUM_DITETAPKAN] 1.GI 150 kV Garung (aset PT Geodipa Energi) beroperasi single phi dan single Busbar. 2.Tidak ada PMT 150 kV arah PLTA Garung</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4427,12 +4494,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] PLTP Dieng dan PLTA Garung dipasok radial 2 line SUTT. Wonosobo- Garung-Dieng dan Wonosobo-Dieng</t>
+          <t>[BELUM_DITETAPKAN] PLTP Dieng dan PLTA Garung dipasok radial 2 line SUTT. Wonosobo- Garung-Dieng dan Wonosobo-Dieng</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4497,12 +4564,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1] 1.Outlet PLTU Cilacap (Cilacap-Rawalo 1,2, Cilacap-Kalibakal, Cilacap-Semen Nusantara) terletak pada tower combined sehingga tidak andal jika terjadi gangguan di ruas tersebut. 2.Intensitas pemeliharaan sangat tinggi karena kondisi polutan pada penghantar outlet PLTU Cilacap</t>
+          <t>[BELUM_DITETAPKAN] 1.Outlet PLTU Cilacap (Cilacap-Rawalo 1,2, Cilacap-Kalibakal, Cilacap-Semen Nusantara) terletak pada tower combined sehingga tidak andal jika terjadi gangguan di ruas tersebut. 2.Intensitas pemeliharaan sangat tinggi karena kondisi polutan pada penghantar outlet PLTU Cilacap</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4532,12 +4599,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Purbalingga-Mrica 1,2 trip 2 sirkit (N-1-1/N- 2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
+          <t>[N-1-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Purbalingga-Mrica 1,2 trip 2 sirkit (N-1-1/N- 2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4602,12 +4669,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
+          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4637,12 +4704,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Semen Nusantara apabila SUTT Kesugihan- Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
+          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Semen Nusantara apabila SUTT Kesugihan- Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
